--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-12-2025.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£9.70</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>£31.50</t>
+          <t>£34.92</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>£38.75</t>
+          <t>£42.50</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>£39.75</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>£43.50</t>
+          <t>£47.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£49.92</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£47.75</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>£45.63</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£47.75</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>£1,155.00</t>
+          <t>£1,275.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>£1,250.00</t>
+          <t>£1,395.00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>£1,225.00</t>
+          <t>£1,395.00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
